--- a/heuristic_analysis2.xlsx
+++ b/heuristic_analysis2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,907 +447,863 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5424731182795699</v>
+        <v>0.5327956989247312</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1277282238006592</v>
+        <v>0.5522884726524353</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4147449135780334</v>
+        <v>-0.0194927453994751</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5370967741935484</v>
+        <v>0.5274193548387097</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1305998861789703</v>
+        <v>0.5415200591087341</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4064969122409821</v>
+        <v>-0.01410073041915894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.5424731182795699</v>
+        <v>0.5338709677419354</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1258746832609177</v>
+        <v>0.5392556190490723</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4165984392166138</v>
+        <v>-0.005384624004364014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.5360215053763441</v>
+        <v>0.513978494623656</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1244782954454422</v>
+        <v>0.5269511938095093</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4115432500839233</v>
+        <v>-0.01297271251678467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.6102150537634409</v>
+        <v>0.5252688172043011</v>
       </c>
       <c r="B6" t="n">
-        <v>0.119095541536808</v>
+        <v>0.5375503301620483</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4911195337772369</v>
+        <v>-0.01228153705596924</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.5940860215053763</v>
+        <v>0.5247311827956989</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1152428090572357</v>
+        <v>0.5286183953285217</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4788432419300079</v>
+        <v>-0.00388723611831665</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.6317204301075269</v>
+        <v>0.524731182795699</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1212661415338516</v>
+        <v>0.5366389155387878</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5104542970657349</v>
+        <v>-0.01190775632858276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.593010752688172</v>
+        <v>0.4956989247311828</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1191438734531403</v>
+        <v>0.4884580671787262</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4738668501377106</v>
+        <v>0.007240861654281616</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.6844086021505376</v>
+        <v>0.4731182795698924</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1265535652637482</v>
+        <v>0.4782289862632751</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5578550100326538</v>
+        <v>-0.005110710859298706</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.6456989247311828</v>
+        <v>0.4521505376344085</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1216962933540344</v>
+        <v>0.4688594341278076</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5240026116371155</v>
+        <v>-0.01670891046524048</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.6252688172043011</v>
+        <v>0.5397849462365591</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1195343285799026</v>
+        <v>0.5703796148300171</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5057345032691956</v>
+        <v>-0.03059464693069458</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.6129032258064517</v>
+        <v>0.5301075268817204</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1223068088293076</v>
+        <v>0.5370304584503174</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4905964136123657</v>
+        <v>-0.00692296028137207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.6629032258064517</v>
+        <v>0.5338709677419354</v>
       </c>
       <c r="B14" t="n">
-        <v>0.120082899928093</v>
+        <v>0.5258004665374756</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5428203344345093</v>
+        <v>0.008070528507232666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.6661290322580645</v>
+        <v>0.621505376344086</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1156695857644081</v>
+        <v>0.5948147177696228</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5504594445228577</v>
+        <v>0.02669066190719604</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.6543010752688172</v>
+        <v>0.5827956989247312</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1152338609099388</v>
+        <v>0.5458363890647888</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5390672087669373</v>
+        <v>0.03695929050445557</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.6440860215053763</v>
+        <v>0.6370967741935483</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1201305836439133</v>
+        <v>0.5824663043022156</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5239554047584534</v>
+        <v>0.05463045835494995</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.6118279569892473</v>
+        <v>0.6295698924731182</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1212410405278206</v>
+        <v>0.5886014699935913</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4905869364738464</v>
+        <v>0.04096841812133789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.5865591397849462</v>
+        <v>0.7059139784946236</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1263947933912277</v>
+        <v>0.7103821039199829</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4601643085479736</v>
+        <v>-0.004468142986297607</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.5994623655913978</v>
+        <v>0.6811827956989247</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1256633698940277</v>
+        <v>0.6935860514640808</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4737990200519562</v>
+        <v>-0.01240324974060059</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.5736559139784946</v>
+        <v>0.6876344086021505</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1239260137081146</v>
+        <v>0.7238097190856934</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4497298896312714</v>
+        <v>-0.03617531061172485</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.5693548387096775</v>
+        <v>0.6688172043010753</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1226699724793434</v>
+        <v>0.7178058624267578</v>
       </c>
       <c r="C22" t="n">
-        <v>0.446684867143631</v>
+        <v>-0.04898864030838013</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.5725806451612904</v>
+        <v>0.7220430107526882</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1234998404979706</v>
+        <v>0.7442306876182556</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4490807950496674</v>
+        <v>-0.02218765020370483</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.5661290322580645</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1259952336549759</v>
+        <v>0.6895230412483215</v>
       </c>
       <c r="C24" t="n">
-        <v>0.440133810043335</v>
+        <v>-0.006189703941345215</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.5553763440860215</v>
+        <v>0.746774193548387</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1240495145320892</v>
+        <v>0.7998147010803223</v>
       </c>
       <c r="C25" t="n">
-        <v>0.43132683634758</v>
+        <v>-0.05304050445556641</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.5446236559139784</v>
+        <v>0.7263440860215054</v>
       </c>
       <c r="B26" t="n">
-        <v>0.124993585050106</v>
+        <v>0.785261869430542</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4196300804615021</v>
+        <v>-0.05891776084899902</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.55</v>
+        <v>0.7349462365591397</v>
       </c>
       <c r="B27" t="n">
-        <v>0.126977726817131</v>
+        <v>0.7350037097930908</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4230222702026367</v>
+        <v>-5.745887756347656e-05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.5306451612903226</v>
+        <v>0.7134408602150537</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1268015950918198</v>
+        <v>0.7151859998703003</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4038435220718384</v>
+        <v>-0.001745164394378662</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.6145161290322581</v>
+        <v>0.7844086021505376</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1330097913742065</v>
+        <v>0.7718796730041504</v>
       </c>
       <c r="C29" t="n">
-        <v>0.48150634765625</v>
+        <v>0.01252895593643188</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.5930107526881719</v>
+        <v>0.7967741935483871</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1261118948459625</v>
+        <v>0.7908660769462585</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4668988287448883</v>
+        <v>0.00590813159942627</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.5779569892473118</v>
+        <v>0.7817204301075268</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1249534785747528</v>
+        <v>0.7825549840927124</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4530034959316254</v>
+        <v>-0.0008345246315002441</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.6080645161290322</v>
+        <v>0.8075268817204301</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1269932985305786</v>
+        <v>0.8455194234848022</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4810712337493896</v>
+        <v>-0.03799253702163696</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.610752688172043</v>
+        <v>0.8080645161290323</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1258302330970764</v>
+        <v>0.8540981411933899</v>
       </c>
       <c r="C33" t="n">
-        <v>0.484922468662262</v>
+        <v>-0.04603362083435059</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.6564516129032258</v>
+        <v>0.7908602150537635</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1272170841693878</v>
+        <v>0.8187705874443054</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5292345285415649</v>
+        <v>-0.02791035175323486</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.6510752688172043</v>
+        <v>0.7715053763440861</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1234476789832115</v>
+        <v>0.8008849620819092</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5276275873184204</v>
+        <v>-0.02937960624694824</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.6602150537634409</v>
+        <v>0.7456989247311828</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1263827085494995</v>
+        <v>0.7806440591812134</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5338323712348938</v>
+        <v>-0.03494513034820557</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.7844086021505376</v>
+        <v>0.7311827956989247</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1284426152706146</v>
+        <v>0.74656081199646</v>
       </c>
       <c r="C37" t="n">
-        <v>0.65596604347229</v>
+        <v>-0.01537799835205078</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.768279569892473</v>
+        <v>0.7446236559139785</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1254734843969345</v>
+        <v>0.7287653088569641</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6428060531616211</v>
+        <v>0.01585835218429565</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.7650537634408602</v>
+        <v>0.8370967741935483</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1266995966434479</v>
+        <v>0.8265337944030762</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6383541822433472</v>
+        <v>0.0105629563331604</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7478494623655915</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1232566088438034</v>
+        <v>0.8146421909332275</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6245928406715393</v>
+        <v>0.002024471759796143</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.7532258064516129</v>
+        <v>0.8983870967741936</v>
       </c>
       <c r="B41" t="n">
-        <v>0.122442252933979</v>
+        <v>0.9184860587120056</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6307835578918457</v>
+        <v>-0.0200989842414856</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.7327956989247312</v>
+        <v>0.8553763440860216</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1276194602251053</v>
+        <v>0.8713414669036865</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6051762700080872</v>
+        <v>-0.01596510410308838</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.7327956989247313</v>
+        <v>0.8263440860215054</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1263998448848724</v>
+        <v>0.8608273863792419</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6063958406448364</v>
+        <v>-0.03448331356048584</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.7037634408602151</v>
+        <v>0.8209677419354838</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1271940171718597</v>
+        <v>0.8422509431838989</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5765694379806519</v>
+        <v>-0.02128320932388306</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.7559139784946237</v>
+        <v>0.8231182795698925</v>
       </c>
       <c r="B45" t="n">
-        <v>0.1202374249696732</v>
+        <v>0.8358470797538757</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6356765627861023</v>
+        <v>-0.01272881031036377</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.7370967741935484</v>
+        <v>0.8134408602150537</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1183687672019005</v>
+        <v>0.8418770432472229</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6187280416488647</v>
+        <v>-0.02843618392944336</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.710752688172043</v>
+        <v>0.8768817204301075</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1164664924144745</v>
+        <v>0.8707611560821533</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5942862033843994</v>
+        <v>0.006120562553405762</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.6978494623655914</v>
+        <v>0.8338709677419355</v>
       </c>
       <c r="B48" t="n">
-        <v>0.115637943148613</v>
+        <v>0.8318828344345093</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5822114944458008</v>
+        <v>0.001988112926483154</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.6860215053763441</v>
+        <v>0.8376344086021505</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1157450079917908</v>
+        <v>0.8926302194595337</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5702764987945557</v>
+        <v>-0.0549958348274231</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.6591397849462366</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1190571784973145</v>
+        <v>0.8446024656295776</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5400826334953308</v>
+        <v>-0.02793580293655396</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.7295698924731182</v>
+        <v>0.817741935483871</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1208029538393021</v>
+        <v>0.7977694869041443</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6087669730186462</v>
+        <v>0.01997244358062744</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.714516129032258</v>
+        <v>0.8419354838709677</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1191538870334625</v>
+        <v>0.7961834669113159</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5953621864318848</v>
+        <v>0.04575198888778687</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.7016129032258065</v>
+        <v>0.8741935483870967</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1144044250249863</v>
+        <v>0.8077784776687622</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5872084498405457</v>
+        <v>0.06641507148742676</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.6887096774193548</v>
+        <v>0.8774193548387097</v>
       </c>
       <c r="B54" t="n">
-        <v>0.118017241358757</v>
+        <v>0.8503331542015076</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5706924200057983</v>
+        <v>0.02708619832992554</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.6672043010752688</v>
+        <v>0.9462365591397851</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1147392243146896</v>
+        <v>0.8894082307815552</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5524650812149048</v>
+        <v>0.05682832002639771</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.6543010752688171</v>
+        <v>0.9268817204301076</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1162642985582352</v>
+        <v>0.8436036109924316</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5380367636680603</v>
+        <v>0.0832781195640564</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.9629032258064516</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1169768795371056</v>
+        <v>0.893374502658844</v>
       </c>
       <c r="C57" t="n">
-        <v>0.5281844139099121</v>
+        <v>0.06952869892120361</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.6505376344086021</v>
+        <v>0.9591397849462365</v>
       </c>
       <c r="B58" t="n">
-        <v>0.1197001188993454</v>
+        <v>0.9085828065872192</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5308374762535095</v>
+        <v>0.05055695772171021</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.7053763440860215</v>
+        <v>0.9623655913978494</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1120173186063766</v>
+        <v>0.9549350738525391</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5933589935302734</v>
+        <v>0.007430493831634521</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.6946236559139786</v>
+        <v>0.9526881720430107</v>
       </c>
       <c r="B60" t="n">
-        <v>0.1108256429433823</v>
+        <v>0.9582893848419189</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5837979912757874</v>
+        <v>-0.005601227283477783</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.6956989247311828</v>
+        <v>0.9784946236559139</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1156983822584152</v>
+        <v>1.013484835624695</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5800005197525024</v>
+        <v>-0.03499019145965576</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.7161290322580646</v>
+        <v>0.9591397849462365</v>
       </c>
       <c r="B62" t="n">
-        <v>0.119724228978157</v>
+        <v>0.9840296506881714</v>
       </c>
       <c r="C62" t="n">
-        <v>0.5964047908782959</v>
+        <v>-0.02488988637924194</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.6870967741935485</v>
+        <v>0.9591397849462366</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1181589215993881</v>
+        <v>1.028398513793945</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5689378380775452</v>
+        <v>-0.06925874948501587</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.6489247311827957</v>
+        <v>0.9467741935483871</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1238828003406525</v>
+        <v>0.9725827574729919</v>
       </c>
       <c r="C64" t="n">
-        <v>0.525041937828064</v>
+        <v>-0.02580857276916504</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.6596774193548388</v>
+        <v>0.9338709677419357</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1292418539524078</v>
+        <v>0.9506332278251648</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5304355621337891</v>
+        <v>-0.01676225662231445</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.6435483870967742</v>
+        <v>0.9215053763440861</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1254431903362274</v>
+        <v>0.9437192678451538</v>
       </c>
       <c r="C66" t="n">
-        <v>0.518105149269104</v>
+        <v>-0.02221387624740601</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.6435483870967742</v>
+        <v>0.8860215053763442</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1214136630296707</v>
+        <v>0.9153876304626465</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5221347212791443</v>
+        <v>-0.029366135597229</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.6521505376344086</v>
+        <v>0.8672043010752688</v>
       </c>
       <c r="B68" t="n">
-        <v>0.120418980717659</v>
+        <v>0.8989965915679932</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5317315459251404</v>
+        <v>-0.0317922830581665</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.6284946236559139</v>
+        <v>0.8596774193548387</v>
       </c>
       <c r="B69" t="n">
-        <v>0.1236323192715645</v>
+        <v>0.9144487380981445</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5048623085021973</v>
+        <v>-0.0547713041305542</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.6102150537634409</v>
+        <v>0.8360215053763441</v>
       </c>
       <c r="B70" t="n">
-        <v>0.122911661863327</v>
+        <v>0.8887104988098145</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4873034060001373</v>
+        <v>-0.05268901586532593</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.6188172043010753</v>
+        <v>0.8258064516129032</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1264105290174484</v>
+        <v>0.865484893321991</v>
       </c>
       <c r="C71" t="n">
-        <v>0.4924066662788391</v>
+        <v>-0.03967845439910889</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.6016129032258065</v>
+        <v>0.8161290322580645</v>
       </c>
       <c r="B72" t="n">
-        <v>0.1238861978054047</v>
+        <v>0.8228871822357178</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4777267277240753</v>
+        <v>-0.006758153438568115</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.606989247311828</v>
+        <v>0.7913978494623656</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1217994689941406</v>
+        <v>0.8189026713371277</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4851897954940796</v>
+        <v>-0.02750480175018311</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.5940860215053764</v>
+        <v>0.7827956989247311</v>
       </c>
       <c r="B74" t="n">
-        <v>0.122862696647644</v>
+        <v>0.8219912648200989</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4712233543395996</v>
+        <v>-0.03919553756713867</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.571505376344086</v>
+        <v>0.7817204301075268</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1218715310096741</v>
+        <v>0.7725979089736938</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4496338367462158</v>
+        <v>0.009122550487518311</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.5897849462365592</v>
+        <v>0.7709677419354839</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1205064132809639</v>
+        <v>0.8077638149261475</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4692785143852234</v>
+        <v>-0.03679609298706055</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.5865591397849462</v>
+        <v>0.7677419354838709</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1211521178483963</v>
+        <v>0.7446838617324829</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4654070138931274</v>
+        <v>0.02305805683135986</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7494623655913978</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1241856664419174</v>
+        <v>0.742575466632843</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4591476321220398</v>
+        <v>0.006886899471282959</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>0.5849462365591398</v>
-      </c>
-      <c r="B79" t="n">
-        <v>0.1259188950061798</v>
-      </c>
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.4590273201465607</v>
+        <v>-0.007981143891811371</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>0.578494623655914</v>
-      </c>
-      <c r="B80" t="n">
-        <v>0.1286669373512268</v>
-      </c>
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.4498276710510254</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>0.5645161290322581</v>
-      </c>
-      <c r="B81" t="n">
-        <v>0.1301894932985306</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.4343266487121582</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>0.5322580645161291</v>
-      </c>
-      <c r="B82" t="n">
-        <v>0.1240264251828194</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0.4082316756248474</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="n">
-        <v>0.5158179998397827</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="n">
-        <v>0.004414331633597612</v>
+        <v>0.001004018587991595</v>
       </c>
     </row>
   </sheetData>
